--- a/parameter_table.xlsx
+++ b/parameter_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas\ribbed-mussel-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F899F-2356-4468-8793-9C3A3DF9F490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA6D8D9-7DE3-451E-8C86-EEFBA7DAE871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20055" yWindow="-16200" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{04490E05-79CD-4735-99E3-5C60614AA183}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{04490E05-79CD-4735-99E3-5C60614AA183}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="186">
   <si>
     <t>Category</t>
   </si>
@@ -1079,27 +1079,6 @@
     <t>Maximum larval size observed during settlement in Chapter 3</t>
   </si>
   <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 2</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 6</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 5</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 4</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 3</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 1</t>
-  </si>
-  <si>
-    <t>Coefficient from fitted model calculated from larval experiment results in Chapter 0</t>
-  </si>
-  <si>
     <t>Exponent from fitted model caculated empirical collector data in Chapter 4</t>
   </si>
   <si>
@@ -1185,6 +1164,9 @@
   </si>
   <si>
     <t>Code</t>
+  </si>
+  <si>
+    <t>Coefficient from fitted model calculated from larval experiment results Chapter 2</t>
   </si>
 </sst>
 </file>
@@ -4172,13 +4154,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>83</v>
@@ -4195,10 +4177,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>9755</v>
+        <v>15000</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
@@ -4218,7 +4200,7 @@
         <v>0.25</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>66</v>
@@ -4238,7 +4220,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
         <v>113</v>
@@ -4258,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
         <v>114</v>
@@ -4278,7 +4260,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
         <v>115</v>
@@ -4298,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
         <v>80</v>
@@ -4318,7 +4300,7 @@
         <v>1.6</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
         <v>81</v>
@@ -4338,7 +4320,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F9" t="s">
         <v>82</v>
@@ -4367,14 +4349,14 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -4388,13 +4370,13 @@
         <v>0.79200000000000004</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -4408,7 +4390,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F13" t="s">
         <v>20</v>
@@ -4432,7 +4414,7 @@
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -4450,7 +4432,7 @@
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -4468,7 +4450,7 @@
         <v>68</v>
       </c>
       <c r="G16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -4486,7 +4468,7 @@
         <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -4500,7 +4482,7 @@
         <v>20</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F18" t="s">
         <v>78</v>
@@ -4538,13 +4520,13 @@
         <v>2.9970920000000002E-2</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
         <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -4562,7 +4544,7 @@
         <v>103</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -4580,7 +4562,7 @@
         <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -4594,13 +4576,13 @@
         <v>10287.72869</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F23" t="s">
         <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -4614,13 +4596,13 @@
         <v>9.2362689999999996E-4</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F24" t="s">
         <v>71</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -4634,13 +4616,13 @@
         <v>3.9558090000000001E-4</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F25" t="s">
         <v>72</v>
       </c>
       <c r="G25" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -4654,13 +4636,13 @@
         <v>1.079747E-7</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F26" t="s">
         <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -4674,13 +4656,13 @@
         <v>1.187E-2</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F27" t="s">
         <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -4694,13 +4676,13 @@
         <v>8.2040000000000002E-2</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F28" t="s">
         <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -4714,7 +4696,7 @@
         <v>0.15</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F29" t="s">
         <v>69</v>
@@ -4734,7 +4716,7 @@
         <v>0.35</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F30" t="s">
         <v>70</v>
@@ -4758,7 +4740,7 @@
         <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -4790,13 +4772,13 @@
         <v>48.25</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -4810,13 +4792,13 @@
         <v>-0.17</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -4830,13 +4812,13 @@
         <v>15.75</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F35" t="s">
         <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -4850,13 +4832,13 @@
         <v>-2.77</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
         <v>74</v>
       </c>
       <c r="G36" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -4870,13 +4852,13 @@
         <v>2.6677177999999999E-2</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
         <v>77</v>
       </c>
       <c r="G37" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -4890,7 +4872,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F38" t="s">
         <v>139</v>
@@ -4904,14 +4886,14 @@
         <v>117</v>
       </c>
       <c r="C39" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -4919,14 +4901,14 @@
         <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D40">
         <v>60</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -4958,7 +4940,7 @@
         <v>1000</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F42" t="s">
         <v>142</v>
